--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="153">
   <si>
     <t>48949</t>
   </si>
@@ -115,34 +115,154 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Unidad de Control Interno</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
+  </si>
+  <si>
+    <t>Coordinaciones Sectoriales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Recuros Materiales y  Servicios Generales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
+  </si>
+  <si>
+    <t>Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
+  </si>
+  <si>
+    <t>Departamento Inventarios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Adminsitrativos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Actividades Deportivas y Culturales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Actividades Paraescolares</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Orientación Educativa y Servicio Social</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Control Escolar</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Seguimiento Académico</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
   </si>
   <si>
     <t>Departamento de Información y Relaciones Públicas</t>
   </si>
   <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2019%20Dpto.%20de%20Informacion%20y%20rel%20publicas.docx</t>
   </si>
   <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Seguimiento Académico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
+    <t>Departamento de Planeación e Infraestructura Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
+  </si>
+  <si>
+    <t>Jefes de Materia</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Bibliotecas y Laboratorios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
   </si>
   <si>
     <t>Departamento de Planes y Programas de Estudio</t>
@@ -151,238 +271,208 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2022%20Dpto.%20planes%20de%20estudio.docx</t>
   </si>
   <si>
-    <t>Departamento de  Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Bibliotecas y Laboratorios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
-  </si>
-  <si>
-    <t>Jefes de Materia</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Orientación Educativa y Servicio Social</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Actividades Paraescolares</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Actividades Deportivas y Culturales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
+  </si>
+  <si>
+    <t>Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
+  </si>
+  <si>
+    <t>Direcciones de Cada Plantel</t>
+  </si>
+  <si>
+    <t>Departamento de programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Dirección Adminsitrativa</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2031%20Direcci%C3%B3n%20Admnistrativa.docx</t>
   </si>
   <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Humanos</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Materiales y Servicios Generales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
-  </si>
-  <si>
-    <t>Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
-  </si>
-  <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
-  </si>
-  <si>
-    <t>Coordinaciones Sectoriales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
-  </si>
-  <si>
-    <t>Direcciones de cada Plantel</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
-  </si>
-  <si>
-    <t>Unidad de Control Interno</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
-  </si>
-  <si>
-    <t>Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación e Infraestrucura Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
-  </si>
-  <si>
-    <t>6AE69612B2206FE709FF5B9177A16DDF</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>FC288B439259A6CC9BDB32DDA04A92C6</t>
-  </si>
-  <si>
-    <t>B56225EEF40693A55193E37E0EB61721</t>
-  </si>
-  <si>
-    <t>06E3DBEF74899E1D4592E778F3642132</t>
-  </si>
-  <si>
-    <t>2D0408F5E07FBA802E4FDADB70791405</t>
-  </si>
-  <si>
-    <t>78697E58B6361B0FDA1CC7319DB226CE</t>
-  </si>
-  <si>
-    <t>8939524FCA5C05D41583E0234EEA5249</t>
-  </si>
-  <si>
-    <t>2D36114475DFCB98F3B59E4F367F4853</t>
-  </si>
-  <si>
-    <t>D87CA9FF921DB810E81BF2515EC1DF60</t>
-  </si>
-  <si>
-    <t>D832E4F07B2B2E7F66E305083AE59B2B</t>
-  </si>
-  <si>
-    <t>C4872DA1DEA936DE2060DDF4C3CF3C09</t>
-  </si>
-  <si>
-    <t>D10810D967F9457FF7B8A4D120B8D704</t>
-  </si>
-  <si>
-    <t>DAD5E47A62E9F1FA0EB5B8BEF55B7BF6</t>
-  </si>
-  <si>
-    <t>5BDFB760FFA95540260130870A627041</t>
-  </si>
-  <si>
-    <t>F46DF60329371ABBA08BE7FEAE245203</t>
-  </si>
-  <si>
-    <t>8770F7C48C7E9A7173A91EB9B5227895</t>
-  </si>
-  <si>
-    <t>8FF0DA4D50CB75DA5DA28DD11B4E2C80</t>
-  </si>
-  <si>
-    <t>D7C05DFC8A2EC18BC0E2A78B21901093</t>
-  </si>
-  <si>
-    <t>62D6AF1D1788130A25A2DA03138BB178</t>
-  </si>
-  <si>
-    <t>E7A8B649573F5AFBB1EBB82F0C9BDA8F</t>
-  </si>
-  <si>
-    <t>A44A80420030847C15AB8A29041487A3</t>
-  </si>
-  <si>
-    <t>4823A9AE1ADBB79D61A9808B1427FC66</t>
-  </si>
-  <si>
-    <t>063D24702D034EA92FC7F7D94A191320</t>
-  </si>
-  <si>
-    <t>AB2D3C2EC23FD4D36563422518CCF68A</t>
-  </si>
-  <si>
-    <t>F2F9203E3DF0E4C63A2833AD1368C5A6</t>
-  </si>
-  <si>
-    <t>8E93C8A2D2873DF2A55B4F96AC132E46</t>
-  </si>
-  <si>
-    <t>D2B3139242EF25CCEE65D78245B2C0CC</t>
-  </si>
-  <si>
-    <t>64B8A0C9542D5D0BB2A81547D81C7A28</t>
+    <t>FFC12BF05ADB2AA2855CBC6DD3DB1177</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>06/10/2023</t>
+  </si>
+  <si>
+    <t>28/04/2021</t>
+  </si>
+  <si>
+    <t>2E93579996A791B8E37F9137A6DB4E2C</t>
+  </si>
+  <si>
+    <t>BC07E67DA82BEC4676A259014B0317F5</t>
+  </si>
+  <si>
+    <t>D3CA6EF9A485A97AACB82B5E24D08524</t>
+  </si>
+  <si>
+    <t>48BD9AE77F52D859FEABE46EAE060392</t>
+  </si>
+  <si>
+    <t>F1CA5B8880BA9307B820EFE518CEA424</t>
+  </si>
+  <si>
+    <t>E9F99198EC3E6166C82F2834CF1A85A7</t>
+  </si>
+  <si>
+    <t>0A5AFC080DEE4423217E9654BA2D423D</t>
+  </si>
+  <si>
+    <t>0B53BA0F6CCA941CA10F6B375D2C615B</t>
+  </si>
+  <si>
+    <t>A698FAEC6AC76092B42FDAE48CAD9818</t>
+  </si>
+  <si>
+    <t>FE4E01334098603ACC0D7CD57DEDC85A</t>
+  </si>
+  <si>
+    <t>F39F110DBD368C2D79BC116C79EEECCF</t>
+  </si>
+  <si>
+    <t>22AC74101945263775C086FC4325CD9E</t>
+  </si>
+  <si>
+    <t>0DB6D95D7F15B901DFA2FFA7A9971C07</t>
+  </si>
+  <si>
+    <t>B3E0F4BB7E17C170C888E75C192A16A5</t>
+  </si>
+  <si>
+    <t>9F0B2F5B1D5F433BE2C4602B1AC506AC</t>
+  </si>
+  <si>
+    <t>44125D771185318260164296B9D70989</t>
+  </si>
+  <si>
+    <t>1D38CD78F1CA253F6E0932F34C4BFC51</t>
+  </si>
+  <si>
+    <t>3BC8AAFE78FA2BE526AEBC7DA57B0116</t>
+  </si>
+  <si>
+    <t>6F936DE030002F30E66551F9A1D3C906</t>
+  </si>
+  <si>
+    <t>896473585E147AC0663A5B075DD45FC8</t>
+  </si>
+  <si>
+    <t>A7255A51CD48E16F9C77CE9CEE88EB6E</t>
+  </si>
+  <si>
+    <t>E67B11B314AC9197719241A268322A71</t>
+  </si>
+  <si>
+    <t>25E9A6F1C5F5119F73890A3B4744EB94</t>
+  </si>
+  <si>
+    <t>0154AD06D288CB065275F94B7CCD9A67</t>
+  </si>
+  <si>
+    <t>BF0D44292C4A7056C01ACF424C72EF2B</t>
+  </si>
+  <si>
+    <t>0D398964B1E398A6E7B62E60320B7FE0</t>
+  </si>
+  <si>
+    <t>E72B882D866EB999FE274774B270A2F2</t>
+  </si>
+  <si>
+    <t>9A98B4C484D9BBF11DF96A1087D80B0C</t>
+  </si>
+  <si>
+    <t>08/10/2023</t>
+  </si>
+  <si>
+    <t>FADB87AE3C2F00E89E1136D17DF70E31</t>
+  </si>
+  <si>
+    <t>9B47FACC6721EEE69F06E7EC7AA4C58F</t>
+  </si>
+  <si>
+    <t>A5494B71C82DA1E6C8C5CB144C9AA13B</t>
+  </si>
+  <si>
+    <t>61D4C45E7E0EBF272269681ADAD9D0EF</t>
+  </si>
+  <si>
+    <t>7CC7075E7248EDA463210B8EDD0A23E9</t>
+  </si>
+  <si>
+    <t>84FFD39CB90A002AC70AD9096444841C</t>
+  </si>
+  <si>
+    <t>821DD28B9695795C5A697D1C091193F2</t>
+  </si>
+  <si>
+    <t>777FD5544D48F249FE26CBBB89C71E02</t>
+  </si>
+  <si>
+    <t>6CEA0FFC2F79FCE3568220B9A1012660</t>
+  </si>
+  <si>
+    <t>354125FF6967C90709EFDF9E366BD717</t>
+  </si>
+  <si>
+    <t>E3A8169EFBE9BBC0E8844B44E4FF7428</t>
+  </si>
+  <si>
+    <t>0CF6038C90E303D904054FBB5DFC1DDA</t>
+  </si>
+  <si>
+    <t>BB34840F3FEA3E617DA721A70BB40478</t>
+  </si>
+  <si>
+    <t>382A2C5CEA569CA752C14E0C57EA6217</t>
+  </si>
+  <si>
+    <t>3DDE0384E839F67305328B314478E250</t>
+  </si>
+  <si>
+    <t>DC65DEE187027F0C6FBC9C601F63E898</t>
+  </si>
+  <si>
+    <t>B707E8241173017B8925B6B84D4DF0AE</t>
+  </si>
+  <si>
+    <t>162E9FFD3033CE8F3F17C0859BE33729</t>
+  </si>
+  <si>
+    <t>0C90AB087490622F0E9E9698D6546AC9</t>
+  </si>
+  <si>
+    <t>D9CDF3DAB4D219B00BB9DF3FA10F7AE1</t>
+  </si>
+  <si>
+    <t>7BA3C31CB51C45D12C0BD8070B71E833</t>
+  </si>
+  <si>
+    <t>8096C403DAAEAE3F38E6335400A8D48F</t>
+  </si>
+  <si>
+    <t>3E65EC9DC1F348B65EC368EBCC509F48</t>
+  </si>
+  <si>
+    <t>B2C0BF6CA4C623D211500B502056E9A8</t>
+  </si>
+  <si>
+    <t>A31BC742FDC6F476E72C604AA8C1EC47</t>
+  </si>
+  <si>
+    <t>CD12B5D280AE5164A1FF4714F0674F9F</t>
+  </si>
+  <si>
+    <t>312D1E5ACBC2801181106A6916A78CD2</t>
   </si>
 </sst>
 </file>
@@ -775,14 +865,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="111.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="188" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
@@ -953,13 +1043,13 @@
         <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>37</v>
@@ -968,7 +1058,7 @@
         <v>95</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>38</v>
@@ -976,34 +1066,34 @@
     </row>
     <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -1011,7 +1101,7 @@
     </row>
     <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
@@ -1023,13 +1113,13 @@
         <v>94</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>37</v>
@@ -1038,7 +1128,7 @@
         <v>95</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>38</v>
@@ -1046,7 +1136,7 @@
     </row>
     <row r="11" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
@@ -1058,13 +1148,13 @@
         <v>94</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>37</v>
@@ -1073,7 +1163,7 @@
         <v>95</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>38</v>
@@ -1081,7 +1171,7 @@
     </row>
     <row r="12" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
@@ -1093,13 +1183,13 @@
         <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>37</v>
@@ -1108,7 +1198,7 @@
         <v>95</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>38</v>
@@ -1116,7 +1206,7 @@
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>33</v>
@@ -1128,13 +1218,13 @@
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>37</v>
@@ -1143,7 +1233,7 @@
         <v>95</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>38</v>
@@ -1151,7 +1241,7 @@
     </row>
     <row r="14" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
@@ -1163,13 +1253,13 @@
         <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>37</v>
@@ -1178,7 +1268,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>38</v>
@@ -1186,7 +1276,7 @@
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>33</v>
@@ -1198,13 +1288,13 @@
         <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>37</v>
@@ -1213,7 +1303,7 @@
         <v>95</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>38</v>
@@ -1221,7 +1311,7 @@
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>33</v>
@@ -1233,13 +1323,13 @@
         <v>94</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>37</v>
@@ -1248,7 +1338,7 @@
         <v>95</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>38</v>
@@ -1256,7 +1346,7 @@
     </row>
     <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -1268,13 +1358,13 @@
         <v>94</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>37</v>
@@ -1283,7 +1373,7 @@
         <v>95</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>38</v>
@@ -1291,7 +1381,7 @@
     </row>
     <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>33</v>
@@ -1303,13 +1393,13 @@
         <v>94</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>37</v>
@@ -1318,7 +1408,7 @@
         <v>95</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>38</v>
@@ -1326,7 +1416,7 @@
     </row>
     <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>33</v>
@@ -1338,13 +1428,13 @@
         <v>94</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>37</v>
@@ -1353,7 +1443,7 @@
         <v>95</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>38</v>
@@ -1361,7 +1451,7 @@
     </row>
     <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>33</v>
@@ -1373,13 +1463,13 @@
         <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>37</v>
@@ -1388,7 +1478,7 @@
         <v>95</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>38</v>
@@ -1396,7 +1486,7 @@
     </row>
     <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>33</v>
@@ -1408,13 +1498,13 @@
         <v>94</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>37</v>
@@ -1423,7 +1513,7 @@
         <v>95</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>38</v>
@@ -1431,7 +1521,7 @@
     </row>
     <row r="22" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>33</v>
@@ -1443,13 +1533,13 @@
         <v>94</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>37</v>
@@ -1458,7 +1548,7 @@
         <v>95</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>38</v>
@@ -1466,7 +1556,7 @@
     </row>
     <row r="23" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
@@ -1478,13 +1568,13 @@
         <v>94</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>37</v>
@@ -1493,7 +1583,7 @@
         <v>95</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>38</v>
@@ -1501,7 +1591,7 @@
     </row>
     <row r="24" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
@@ -1513,13 +1603,13 @@
         <v>94</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>37</v>
@@ -1528,7 +1618,7 @@
         <v>95</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>38</v>
@@ -1536,7 +1626,7 @@
     </row>
     <row r="25" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
@@ -1548,13 +1638,13 @@
         <v>94</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>37</v>
@@ -1563,7 +1653,7 @@
         <v>95</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>38</v>
@@ -1571,7 +1661,7 @@
     </row>
     <row r="26" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>33</v>
@@ -1583,13 +1673,13 @@
         <v>94</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>37</v>
@@ -1598,7 +1688,7 @@
         <v>95</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>38</v>
@@ -1606,7 +1696,7 @@
     </row>
     <row r="27" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>33</v>
@@ -1618,13 +1708,13 @@
         <v>94</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>37</v>
@@ -1633,7 +1723,7 @@
         <v>95</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>38</v>
@@ -1641,7 +1731,7 @@
     </row>
     <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>33</v>
@@ -1653,13 +1743,13 @@
         <v>94</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>37</v>
@@ -1668,7 +1758,7 @@
         <v>95</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>38</v>
@@ -1676,7 +1766,7 @@
     </row>
     <row r="29" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>33</v>
@@ -1688,13 +1778,13 @@
         <v>94</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>37</v>
@@ -1703,7 +1793,7 @@
         <v>95</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>38</v>
@@ -1711,7 +1801,7 @@
     </row>
     <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>33</v>
@@ -1723,13 +1813,13 @@
         <v>94</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>37</v>
@@ -1738,7 +1828,7 @@
         <v>95</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>38</v>
@@ -1746,7 +1836,7 @@
     </row>
     <row r="31" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>33</v>
@@ -1758,13 +1848,13 @@
         <v>94</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>37</v>
@@ -1773,7 +1863,7 @@
         <v>95</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>38</v>
@@ -1781,7 +1871,7 @@
     </row>
     <row r="32" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>33</v>
@@ -1793,13 +1883,13 @@
         <v>94</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>37</v>
@@ -1808,7 +1898,7 @@
         <v>95</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>38</v>
@@ -1816,7 +1906,7 @@
     </row>
     <row r="33" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>33</v>
@@ -1828,13 +1918,13 @@
         <v>94</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>37</v>
@@ -1843,7 +1933,7 @@
         <v>95</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>38</v>
@@ -1851,7 +1941,7 @@
     </row>
     <row r="34" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>33</v>
@@ -1863,13 +1953,13 @@
         <v>94</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>37</v>
@@ -1878,7 +1968,7 @@
         <v>95</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>38</v>
@@ -1886,7 +1976,7 @@
     </row>
     <row r="35" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>33</v>
@@ -1898,24 +1988,1004 @@
         <v>94</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="F60" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K35" s="2" t="s">
+      <c r="F62" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K63" s="2" t="s">
         <v>38</v>
       </c>
     </row>
